--- a/TESTS/zlit_6_dikens.xlsx
+++ b/TESTS/zlit_6_dikens.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Чарльз Діккенс — видатний англійський письменник XIX ст. відомий своєю соціальною прозою</t>
+          <t>Чарльз Діккенс</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>На Різдво у Лондоні — свято є символом доброти щедрості і людяності</t>
+          <t>На Різдво у Лондоні</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Різдвяна повість — короткий фантастичний твір з моральним посланням що Діккенс ввів у традицію</t>
+          <t>Різдвяна повість</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ебенезер Скрудж — жадібний старий лихвар що зневажає бідних і ненавидить Різдво</t>
+          <t>Ебенезер Скрудж</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -771,6 +796,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>«Балаканина!» (Bah Humbug!) — він зневажливо відкидає всі різдвяні привітання</t>
+          <t>«Балаканина!» (Bah Humbug!)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -855,6 +890,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -897,6 +937,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Його власне дитинство і молодість коли він ще вмів радіти і любити — до того як жадібність знищила його душу</t>
+          <t>Його власне дитинство і молодість коли він ще вмів радіти і любити</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Що Дух Різдва минулого показав Скруджу про його юність?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його весілля</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Веселе різдвяне свято у його колишнього роботодавця Феззівіга</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його школу</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Його батьків</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Яким був Феззівіг як роботодавець, на відміну від дорослого Скруджа?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Таким же скупим</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Щедрим і добрим — влаштовував свято для всіх своїх працівників</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Жорстоким</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Байдужим</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Кого ще показав Дух Різдва минулого — кохану Скруджа, з якою він розійшовся?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його сестру</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дівчину Белль, яка покинула його, бо він обрав гроші замість любові</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його матір</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Подругу дитинства</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Яким був різдвяний обід родини Крекітів, попри їхню бідність?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сумним і скупим</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Скромним, але теплим і радісним — з гусаком та пудингом</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Багатим</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони взагалі не святкували</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що сказав Тін Тім за різдвяним столом, що зворушило Скруджа?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Подякував за їжу</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Виголосив тост «Хай Бог благословить нас усіх!», попри власну хворобу</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Заплакав</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не сказав</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Як Боб Крекіт говорив про свого начальника, містера Скруджа, за столом?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лихословив про нього</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Запропонував випити за його здоров'я, хоч дружина й була проти</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Нічого про нього не сказав</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Прокляв його</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Хто такий Фред у повісті?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Слуга Скруджа</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Племінник Скруджа, який щиро любить дядька і щороку запрошує його на Різдво</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сусід</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Колишній компаньйон</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Як Скрудж відповів на запрошення Фреда на початку повісті?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Радо погодився</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Грубо відмовив, назвавши Різдво «дурницею»</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Не відповів</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Образився</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що Дух Різдва сьогодення показав Скруджу на вечірці у Фреда?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сварку гостей</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Як гості жартома, без злості, обговорюють дивакуватого дядька, але все одно п'ють за його здоров'я</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Як усі забули про Скруджа</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Порожній будинок</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Яким Дух Різдва майбутнього показав себе Скруджу?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Веселим і балакучим</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Мовчазною темною постаттю в каптурі, що лише вказувала рукою</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Маленькою дитиною</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Старим лікарем</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що Скрудж побачив, коли Дух показав кімнату, де говорили про чиюсь смерть?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Усі сумували щиро</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Знайомі байдуже й навіть із полегшенням обговорювали смерть багатія, нікому не шкода</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Велике похоронне свято</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Порожню кімнату</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Чию могилу зрештою показав Скруджу Дух Різдва майбутнього?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Могилу Марлі</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Його власну могилу з його іменем</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Могилу Тін Тіма</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Безіменну могилу</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Що відчув Скрудж, прокинувшись у своєму ліжку після візиту трьох Духів?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Байдужість</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Неймовірну радість і полегшення, що в нього ще є час усе змінити</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Страх</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він не пам'ятав нічого</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Що першим зробив Скрудж, зрозумівши, що це досі різдвяний ранок?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Заснув знову</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Радісно засміявся і почав вигукувати поздоровлення з Різдвом</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Розгнівався</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Пішов на роботу мовчки</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Кого Скрудж попросив хлопчика на вулиці купити для родини Крекітів?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Дрова</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Найбільшу різдвяну індичку, яку тільки можна знайти</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Подарунки дітям</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вино</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Куди Скрудж пішов одразу після того, як відправив індичку Крекітам?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>До церкви помолитися</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>До Фреда на різдвяний обід, прийнявши давнє запрошення</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Спати</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>До контори</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Як Фред і його гості зустріли Скруджа, коли він несподівано прийшов?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Прогнали його</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Здивовано, але радо й тепло прийняли його</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Не впізнали</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Розсердились</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Яким став сам Скрудж у спілкуванні з людьми після того дня?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишився таким же черствим</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Веселим, щедрим і доброзичливим до всіх</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дуже сумним</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Замкнутим, як і раніше</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Що зробив Скрудж наступного дня, коли Боб Крекіт спізнився на роботу?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Покарав його штрафом</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Спершу прикинувся суворим, а потім оголосив, що підвищить йому платню</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вигнав його</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не сказав</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Як змінилося ставлення Скруджа до Тін Тіма та родини Крекітів надалі?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Не змінилось</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він став для Тіма майже другим батьком і допомагав родині</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він забув про них</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він почав їх уникати</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Чим завершується повість «Різдвяна пісня в прозі»?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Скрудж помирає</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Скрудж стає прикладом того, як по-справжньому варто святкувати Різдво — щедро і з добрим серцем</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Скрудж розчаровується у людях</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не змінюється</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яку соціальну критику містить «Різдвяна пісня»?</t>
+          <t>«Різдвяна пісня в прозі» містить критику байдужості багатих до бідних у вікторіанській Англії.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яку традицію ввів Діккенс у літературу своєю «Різдвяною піснею»?</t>
+          <t>Діккенс однією з перших творів зробив популярним сучасний образ святкового, сімейного Різдва.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Чому «Різдвяна пісня» вважається одним з найвпливовіших різдвяних творів?</t>
+          <t>«Різдвяна пісня» вважається впливовою, бо це єдина різдвяна історія, написана англійською мовою.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яка трансформація відбувається зі Скруджем наприкінці повісті?</t>
+          <t>Завдяки візитам трьох Духів Скрудж перетворюється зі скупого черствого старого на щедру й добру людину.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2244,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея «Різдвяної пісні»?</t>
+          <t>Головна ідея повісті — гроші важливіші за стосунки з людьми.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Що символізує Різдво у повісті Діккенса?</t>
+          <t>Різдво у повісті символізує можливість змінитися, прощення і людську доброту.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які три Духи відвідують Скруджа?</t>
+          <t>Що Скрудж зробив наступного дня після візитів Духів?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Дух Різдва минулого</t>
+          <t>Відправив індичку родині Крекітів</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Дух Різдва сьогодення</t>
+          <t>Пішов до Фреда на обід</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Дух літа майбутнього</t>
+          <t>Звільнив Боба Крекіта</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Дух Різдва майбутнього</t>
+          <t>Пообіцяв підвищити платню Бобу</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2295,6 +2492,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Хворий маленький син Боба Крекіта — символ невинності і страждань бідних дітей</t>
+          <t>Хворий маленький син Боба Крекіта</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
